--- a/Results/filewise_annotation_agreement_results.xlsx
+++ b/Results/filewise_annotation_agreement_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khushi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCABD1D0-1B92-4E36-A3B6-308CE27D6497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F6E778-A2F5-4B84-88D8-2B4EFF911D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="52">
   <si>
     <t>discipline</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>A22</t>
+  </si>
+  <si>
+    <t>Author</t>
   </si>
 </sst>
 </file>
@@ -537,12 +540,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
